--- a/r1/gen/r1-finalReport.xlsx
+++ b/r1/gen/r1-finalReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fedev\Documents\UNICAM\Phd\unmock\r1\gen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F402EB-564C-44D3-AB14-DFD3A0656FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DBFADA-BF3C-4F2A-8187-4C5863E38234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{398B28D4-6843-470D-81CE-51D800613A8C}"/>
   </bookViews>
@@ -187,18 +187,6 @@
     <t>testAddIdentityToGrpcRequestWhenNotSupport</t>
   </si>
   <si>
-    <t>Argument matchers in thenReturn</t>
-  </si>
-  <si>
-    <t>Transformed argument matchers in thenReturn</t>
-  </si>
-  <si>
-    <t>Transformed argument matchers in thenReturn with syntax errors</t>
-  </si>
-  <si>
-    <t>Transformed argument matcher in thenReturn with semantic errors</t>
-  </si>
-  <si>
     <t>0.023829</t>
   </si>
   <si>
@@ -257,6 +245,18 @@
   </si>
   <si>
     <t>0.012227</t>
+  </si>
+  <si>
+    <t>Argument matchers in stub</t>
+  </si>
+  <si>
+    <t>Transformed argument matchers in stub</t>
+  </si>
+  <si>
+    <t>Transformed argument matchers in stub with syntax errors</t>
+  </si>
+  <si>
+    <t>Transformed argument matcher in stub with semantic errors</t>
   </si>
 </sst>
 </file>
@@ -948,7 +948,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1006,7 +1006,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1035,7 +1035,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1328,33 +1328,33 @@
         <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="H23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -1369,16 +1369,16 @@
         <v>22</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1513,13 +1513,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1528,10 +1528,10 @@
         <v>N.1</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1540,10 +1540,10 @@
         <v>N.2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1552,10 +1552,10 @@
         <v>N.3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1564,10 +1564,10 @@
         <v>N.4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
